--- a/SKU_Transition.xlsx
+++ b/SKU_Transition.xlsx
@@ -2,21 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RM Planning\Digitization\RM 8 Reasons\New 8 Reasons Tool\SATL Nov25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A2556E-14E3-4B7A-B412-21A48B372D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216AC6B5-137C-4F90-A032-6B2AB4A39A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AAE75852-6E75-47B9-9E11-7357059B2E3A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$92</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,45 +34,357 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="4">
-  <si>
-    <t>Phase-Out RM Code</t>
-  </si>
-  <si>
-    <t>Phase-In RM Code</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="111">
+  <si>
+    <t>Plant Name</t>
+  </si>
+  <si>
+    <t>Plant Code</t>
+  </si>
+  <si>
+    <t>RM Code</t>
+  </si>
+  <si>
+    <t>RM Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Cycle</t>
+  </si>
+  <si>
+    <t>Aurangabad</t>
   </si>
   <si>
     <t>A350</t>
   </si>
   <si>
-    <t>Plant Code</t>
+    <t>CODE 4</t>
+  </si>
+  <si>
+    <t>F-PIG/OILS/CHEM</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>CODE , 567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import </t>
+  </si>
+  <si>
+    <t>CODE , 1044</t>
+  </si>
+  <si>
+    <t>CODE , 1011</t>
+  </si>
+  <si>
+    <t>CODE 1144</t>
+  </si>
+  <si>
+    <t>CODE , 1171</t>
+  </si>
+  <si>
+    <t>CODE - 1371</t>
+  </si>
+  <si>
+    <t>CODE - SILANIC</t>
+  </si>
+  <si>
+    <t>CODE , ADAMAX</t>
+  </si>
+  <si>
+    <t>CODE - BETHUNIC</t>
+  </si>
+  <si>
+    <t>CODE-CITAX</t>
+  </si>
+  <si>
+    <t>CODE , DIROSIC</t>
+  </si>
+  <si>
+    <t>CODE , GOODINE</t>
+  </si>
+  <si>
+    <t>CODE , HAWKAX</t>
+  </si>
+  <si>
+    <t>CODE , RENARDIC</t>
+  </si>
+  <si>
+    <t>CODE , KERWAX</t>
+  </si>
+  <si>
+    <t>CODE , KLINGIC</t>
+  </si>
+  <si>
+    <t>Import</t>
+  </si>
+  <si>
+    <t>CODE , LEIBAX</t>
+  </si>
+  <si>
+    <t>CODE - LICKIC</t>
+  </si>
+  <si>
+    <t>CODE - MILNIC</t>
+  </si>
+  <si>
+    <t>CODE , MULTINE</t>
+  </si>
+  <si>
+    <t>LUMTINE</t>
+  </si>
+  <si>
+    <t>CODE , NAILAX</t>
+  </si>
+  <si>
+    <t>CODE , OLIVAX</t>
+  </si>
+  <si>
+    <t>CODE , PHENAX</t>
+  </si>
+  <si>
+    <t>CODE , SARDINE</t>
+  </si>
+  <si>
+    <t>CODE , STERAX</t>
+  </si>
+  <si>
+    <t>CODE , SURFAX</t>
+  </si>
+  <si>
+    <t>CODE , SYDNINE</t>
+  </si>
+  <si>
+    <t>Local (Imported)</t>
+  </si>
+  <si>
+    <t>CODE , THIELIC</t>
+  </si>
+  <si>
+    <t>NABUCIC</t>
+  </si>
+  <si>
+    <t>KANZIC</t>
+  </si>
+  <si>
+    <t>CODE , MULTRAX</t>
+  </si>
+  <si>
+    <t>CODE , WIROTHIC</t>
+  </si>
+  <si>
+    <t>CODE , ZONFLAX</t>
+  </si>
+  <si>
+    <t>TROWMIC</t>
+  </si>
+  <si>
+    <t>CODE , LAMBRAX</t>
+  </si>
+  <si>
+    <t>GALINDIC</t>
+  </si>
+  <si>
+    <t>CODE , 210</t>
+  </si>
+  <si>
+    <t>CODE210</t>
+  </si>
+  <si>
+    <t>CODE , BLUTRIC</t>
+  </si>
+  <si>
+    <t>CODE , CHUTIC</t>
+  </si>
+  <si>
+    <t>KORNATIC</t>
+  </si>
+  <si>
+    <t>CODE6917</t>
+  </si>
+  <si>
+    <t>CODE , 9071</t>
+  </si>
+  <si>
+    <t>CROYDAX</t>
+  </si>
+  <si>
+    <t>CODE , HOOVERIC</t>
+  </si>
+  <si>
+    <t>BOEHNITE</t>
+  </si>
+  <si>
+    <t>CHRISMIC</t>
+  </si>
+  <si>
+    <t>ELBLIC</t>
+  </si>
+  <si>
+    <t>CODE , BIJINIC</t>
+  </si>
+  <si>
+    <t>CODE , 228 / N550</t>
+  </si>
+  <si>
+    <t>A-CARBON BLACK</t>
+  </si>
+  <si>
+    <t>405 / N220</t>
+  </si>
+  <si>
+    <t>CODE , 510 / N660</t>
+  </si>
+  <si>
+    <t>CODE , 599 / N347</t>
+  </si>
+  <si>
+    <t>CODE , 630 / N326</t>
+  </si>
+  <si>
+    <t>CODE , BINIC</t>
+  </si>
+  <si>
+    <t>G-SYNTHETIC RUBBER</t>
+  </si>
+  <si>
+    <t>CODE , RIONIC</t>
+  </si>
+  <si>
+    <t>CODE , BUD1208</t>
+  </si>
+  <si>
+    <t>CODE-CHEFFIC</t>
+  </si>
+  <si>
+    <t>CODE , COMODIC</t>
+  </si>
+  <si>
+    <t>CODE , SLF33H23</t>
+  </si>
+  <si>
+    <t>CODE , BUD4001</t>
+  </si>
+  <si>
+    <t>CODE , SCIEKIC</t>
+  </si>
+  <si>
+    <t>CODE , BUD1223</t>
+  </si>
+  <si>
+    <t>CODE , BUD1207</t>
+  </si>
+  <si>
+    <t>SANTOSIC</t>
+  </si>
+  <si>
+    <t>DRIFTIC</t>
+  </si>
+  <si>
+    <t>TAKUMIC</t>
+  </si>
+  <si>
+    <t>TROOPIC</t>
+  </si>
+  <si>
+    <t>PREVELIC</t>
+  </si>
+  <si>
+    <t>CODE , NAPLO</t>
+  </si>
+  <si>
+    <t>D-NATURAL RUBBER</t>
+  </si>
+  <si>
+    <t>KARSO</t>
+  </si>
+  <si>
+    <t>NOLO</t>
+  </si>
+  <si>
+    <t>CODE , NIMBO</t>
+  </si>
+  <si>
+    <t>I-47-LZ-NY CHAFER FABRIC</t>
+  </si>
+  <si>
+    <t>C-FABRIC</t>
+  </si>
+  <si>
+    <t>CK  BEAD WRAP</t>
+  </si>
+  <si>
+    <t>CODE , BN32JA</t>
+  </si>
+  <si>
+    <t>CODE , CE16WA</t>
+  </si>
+  <si>
+    <t>NC30ZO PINK DIP</t>
+  </si>
+  <si>
+    <t>NG30JA (Black Dip)</t>
+  </si>
+  <si>
+    <t>Code 9481</t>
+  </si>
+  <si>
+    <t>EVRIC</t>
+  </si>
+  <si>
+    <t>TC28CX (Pink Dip)</t>
+  </si>
+  <si>
+    <t>TM26CX (PINK DIP)</t>
+  </si>
+  <si>
+    <t>TU32CX (Pink Dip)</t>
+  </si>
+  <si>
+    <t>NC16ZM (Pink Dip)</t>
+  </si>
+  <si>
+    <t>WY</t>
+  </si>
+  <si>
+    <t>B-CREEL WIRE</t>
+  </si>
+  <si>
+    <t>UW STEEL CORD</t>
+  </si>
+  <si>
+    <t>WL STEEL CORD</t>
+  </si>
+  <si>
+    <t>CODE , JH</t>
+  </si>
+  <si>
+    <t>E-OTHERS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,32 +396,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED7D31"/>
-        <bgColor rgb="FFFF8080"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -112,83 +415,13 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFED7D31"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -201,9 +434,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -211,39 +444,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -295,7 +528,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -347,7 +580,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -406,13 +639,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -421,6 +647,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -485,109 +718,5472 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D08FA1-B08E-4833-90E5-CCEB95A1E5DF}">
+  <dimension ref="A1:S92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>202411</v>
+      </c>
+      <c r="I1">
+        <v>202412</v>
+      </c>
+      <c r="J1">
+        <v>202501</v>
+      </c>
+      <c r="K1">
+        <v>202502</v>
+      </c>
+      <c r="L1">
+        <v>202503</v>
+      </c>
+      <c r="M1">
+        <v>202504</v>
+      </c>
+      <c r="N1">
+        <v>202505</v>
+      </c>
+      <c r="O1">
+        <v>202506</v>
+      </c>
+      <c r="P1">
+        <v>202507</v>
+      </c>
+      <c r="Q1">
+        <v>202508</v>
+      </c>
+      <c r="R1">
+        <v>202509</v>
+      </c>
+      <c r="S1">
+        <v>202510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1100032</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>24373.392300921423</v>
+      </c>
+      <c r="I2">
+        <v>22427.733536942542</v>
+      </c>
+      <c r="J2">
+        <v>27427.80646560578</v>
+      </c>
+      <c r="K2">
+        <v>25913.289814155298</v>
+      </c>
+      <c r="L2">
+        <v>27915.122041052087</v>
+      </c>
+      <c r="M2">
+        <v>27552.862266352226</v>
+      </c>
+      <c r="N2">
+        <v>27622.487837203837</v>
+      </c>
+      <c r="O2">
+        <v>27853.89169082174</v>
+      </c>
+      <c r="P2">
+        <v>29771.86815252528</v>
+      </c>
+      <c r="Q2">
+        <v>28670.354050031663</v>
+      </c>
+      <c r="R2">
+        <v>28241.05127409584</v>
+      </c>
+      <c r="S2">
+        <v>25986.087249950448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1100033</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>60</v>
+      </c>
+      <c r="H3">
+        <v>2958.1447684685695</v>
+      </c>
+      <c r="I3">
+        <v>3123.3641576101941</v>
+      </c>
+      <c r="J3">
+        <v>4290.9628462023047</v>
+      </c>
+      <c r="K3">
+        <v>3479.3849477020503</v>
+      </c>
+      <c r="L3">
+        <v>3526.8778939743829</v>
+      </c>
+      <c r="M3">
+        <v>3670.3043843916662</v>
+      </c>
+      <c r="N3">
+        <v>3894.6773426854224</v>
+      </c>
+      <c r="O3">
+        <v>3946.1431229987807</v>
+      </c>
+      <c r="P3">
+        <v>4467.6041136529857</v>
+      </c>
+      <c r="Q3">
+        <v>4521.6381876361929</v>
+      </c>
+      <c r="R3">
+        <v>4578.0369889260619</v>
+      </c>
+      <c r="S3">
+        <v>3494.0632359717738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>1100070</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>7831.9055354039901</v>
+      </c>
+      <c r="I4">
+        <v>7583.4647677324983</v>
+      </c>
+      <c r="J4">
+        <v>9308.9437431173501</v>
+      </c>
+      <c r="K4">
+        <v>8575.1452061678156</v>
+      </c>
+      <c r="L4">
+        <v>9316.3130406559412</v>
+      </c>
+      <c r="M4">
+        <v>9257.9487109302863</v>
+      </c>
+      <c r="N4">
+        <v>9106.6964923939522</v>
+      </c>
+      <c r="O4">
+        <v>9396.1079594555104</v>
+      </c>
+      <c r="P4">
+        <v>10204.326406892267</v>
+      </c>
+      <c r="Q4">
+        <v>9238.531800544235</v>
+      </c>
+      <c r="R4">
+        <v>9621.7418482710546</v>
+      </c>
+      <c r="S4">
+        <v>8808.1453306675376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>1100194</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>71572.266973770165</v>
+      </c>
+      <c r="I5">
+        <v>66508.414871867775</v>
+      </c>
+      <c r="J5">
+        <v>81259.59803476154</v>
+      </c>
+      <c r="K5">
+        <v>75821.017081517421</v>
+      </c>
+      <c r="L5">
+        <v>81484.493808721891</v>
+      </c>
+      <c r="M5">
+        <v>80627.583741261071</v>
+      </c>
+      <c r="N5">
+        <v>79298.850035100622</v>
+      </c>
+      <c r="O5">
+        <v>80879.315072550919</v>
+      </c>
+      <c r="P5">
+        <v>87049.584824808262</v>
+      </c>
+      <c r="Q5">
+        <v>82236.998736778187</v>
+      </c>
+      <c r="R5">
+        <v>81534.360356665682</v>
+      </c>
+      <c r="S5">
+        <v>74525.304668742174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1100076</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>18390.108756542733</v>
+      </c>
+      <c r="I6">
+        <v>17030.396310981967</v>
+      </c>
+      <c r="J6">
+        <v>20715.539371415871</v>
+      </c>
+      <c r="K6">
+        <v>19348.146887578816</v>
+      </c>
+      <c r="L6">
+        <v>20737.019838671473</v>
+      </c>
+      <c r="M6">
+        <v>20608.988648132738</v>
+      </c>
+      <c r="N6">
+        <v>20394.182940175058</v>
+      </c>
+      <c r="O6">
+        <v>20866.076811403123</v>
+      </c>
+      <c r="P6">
+        <v>22188.604901141698</v>
+      </c>
+      <c r="Q6">
+        <v>21082.998855276648</v>
+      </c>
+      <c r="R6">
+        <v>20739.887841765329</v>
+      </c>
+      <c r="S6">
+        <v>19086.448764346129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1100029</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>48040.257746644842</v>
+      </c>
+      <c r="I7">
+        <v>48075.489572408245</v>
+      </c>
+      <c r="J7">
+        <v>60609.755791784592</v>
+      </c>
+      <c r="K7">
+        <v>65591.464030789997</v>
+      </c>
+      <c r="L7">
+        <v>67721.243725054097</v>
+      </c>
+      <c r="M7">
+        <v>60401.59539438357</v>
+      </c>
+      <c r="N7">
+        <v>66580.349973169315</v>
+      </c>
+      <c r="O7">
+        <v>77648.034789948826</v>
+      </c>
+      <c r="P7">
+        <v>95492.76511495946</v>
+      </c>
+      <c r="Q7">
+        <v>81221.580021928326</v>
+      </c>
+      <c r="R7">
+        <v>83296.384031437352</v>
+      </c>
+      <c r="S7">
+        <v>65126.810650991218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1100357</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>177666.11295946085</v>
+      </c>
+      <c r="I8">
+        <v>172840.66206194472</v>
+      </c>
+      <c r="J8">
+        <v>204820.45829206196</v>
+      </c>
+      <c r="K8">
+        <v>168065.45181550222</v>
+      </c>
+      <c r="L8">
+        <v>182722.17503693415</v>
+      </c>
+      <c r="M8">
+        <v>170848.51693438424</v>
+      </c>
+      <c r="N8">
+        <v>175497.25154862789</v>
+      </c>
+      <c r="O8">
+        <v>186355.97667088441</v>
+      </c>
+      <c r="P8">
+        <v>208212.67314315506</v>
+      </c>
+      <c r="Q8">
+        <v>202309.08992720395</v>
+      </c>
+      <c r="R8">
+        <v>198339.96593489949</v>
+      </c>
+      <c r="S8">
+        <v>162262.45499085356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>1100539</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9">
+        <v>27484.794176574924</v>
+      </c>
+      <c r="I9">
+        <v>26898.934103756128</v>
+      </c>
+      <c r="J9">
+        <v>30244.950431264358</v>
+      </c>
+      <c r="K9">
+        <v>26931.060091847099</v>
+      </c>
+      <c r="L9">
+        <v>28375.414791034564</v>
+      </c>
+      <c r="M9">
+        <v>27343.46134124936</v>
+      </c>
+      <c r="N9">
+        <v>25825.638917988985</v>
+      </c>
+      <c r="O9">
+        <v>25170.36218651212</v>
+      </c>
+      <c r="P9">
+        <v>28863.884056327421</v>
+      </c>
+      <c r="Q9">
+        <v>26063.96944421616</v>
+      </c>
+      <c r="R9">
+        <v>27075.333243029945</v>
+      </c>
+      <c r="S9">
+        <v>23831.586212731301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>1100038</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
+      </c>
+      <c r="H10">
+        <v>4065.3106378553634</v>
+      </c>
+      <c r="I10">
+        <v>4010.2857850406867</v>
+      </c>
+      <c r="J10">
+        <v>4561.6706710392464</v>
+      </c>
+      <c r="K10">
+        <v>4036.784013835977</v>
+      </c>
+      <c r="L10">
+        <v>4349.8349939933869</v>
+      </c>
+      <c r="M10">
+        <v>4199.5492805127888</v>
+      </c>
+      <c r="N10">
+        <v>4315.9947257634376</v>
+      </c>
+      <c r="O10">
+        <v>4347.0811682217227</v>
+      </c>
+      <c r="P10">
+        <v>4576.0030278454688</v>
+      </c>
+      <c r="Q10">
+        <v>4413.5805272398702</v>
+      </c>
+      <c r="R10">
+        <v>4444.1396839712079</v>
+      </c>
+      <c r="S10">
+        <v>3925.3553904231071</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>1100935</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>19482.641062849347</v>
+      </c>
+      <c r="I11">
+        <v>17644.54620870719</v>
+      </c>
+      <c r="J11">
+        <v>22887.842535779342</v>
+      </c>
+      <c r="K11">
+        <v>21215.13608998675</v>
+      </c>
+      <c r="L11">
+        <v>20268.560761661854</v>
+      </c>
+      <c r="M11">
+        <v>20604.322947863919</v>
+      </c>
+      <c r="N11">
+        <v>23183.095815364366</v>
+      </c>
+      <c r="O11">
+        <v>24053.716693560818</v>
+      </c>
+      <c r="P11">
+        <v>25321.413525519052</v>
+      </c>
+      <c r="Q11">
+        <v>24857.708366446423</v>
+      </c>
+      <c r="R11">
+        <v>24613.972209929565</v>
+      </c>
+      <c r="S11">
+        <v>23854.734380001159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>1100072</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>60</v>
+      </c>
+      <c r="H12">
+        <v>4498.6402421785542</v>
+      </c>
+      <c r="I12">
+        <v>4473.4463422107738</v>
+      </c>
+      <c r="J12">
+        <v>5180.1113960997409</v>
+      </c>
+      <c r="K12">
+        <v>4573.0989409107906</v>
+      </c>
+      <c r="L12">
+        <v>4913.4856710018648</v>
+      </c>
+      <c r="M12">
+        <v>4748.7577701377886</v>
+      </c>
+      <c r="N12">
+        <v>4840.3392921971454</v>
+      </c>
+      <c r="O12">
+        <v>4866.7799250466032</v>
+      </c>
+      <c r="P12">
+        <v>5263.8926804969924</v>
+      </c>
+      <c r="Q12">
+        <v>5011.6144465673306</v>
+      </c>
+      <c r="R12">
+        <v>5128.365412260996</v>
+      </c>
+      <c r="S12">
+        <v>4468.4233948334704</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>1100067</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>60</v>
+      </c>
+      <c r="H13">
+        <v>255.9180472016011</v>
+      </c>
+      <c r="I13">
+        <v>278.78010040272108</v>
+      </c>
+      <c r="J13">
+        <v>345.36565438080402</v>
+      </c>
+      <c r="K13">
+        <v>268.69224351228559</v>
+      </c>
+      <c r="L13">
+        <v>289.00764626268568</v>
+      </c>
+      <c r="M13">
+        <v>300.80780958969689</v>
+      </c>
+      <c r="N13">
+        <v>311.8344306582909</v>
+      </c>
+      <c r="O13">
+        <v>310.0475518806698</v>
+      </c>
+      <c r="P13">
+        <v>298.50302792347884</v>
+      </c>
+      <c r="Q13">
+        <v>297.65604074929792</v>
+      </c>
+      <c r="R13">
+        <v>272.10439435170474</v>
+      </c>
+      <c r="S13">
+        <v>244.59643253159049</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>1100042</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14">
+        <v>22882.082228224714</v>
+      </c>
+      <c r="I14">
+        <v>23062.266300609735</v>
+      </c>
+      <c r="J14">
+        <v>26153.645479990806</v>
+      </c>
+      <c r="K14">
+        <v>22891.394621355081</v>
+      </c>
+      <c r="L14">
+        <v>24406.136321196402</v>
+      </c>
+      <c r="M14">
+        <v>23874.871982029821</v>
+      </c>
+      <c r="N14">
+        <v>24290.086032216335</v>
+      </c>
+      <c r="O14">
+        <v>24683.787544080136</v>
+      </c>
+      <c r="P14">
+        <v>26706.030414209967</v>
+      </c>
+      <c r="Q14">
+        <v>25187.504275862677</v>
+      </c>
+      <c r="R14">
+        <v>25873.265319156821</v>
+      </c>
+      <c r="S14">
+        <v>22156.136565303994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>1100066</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>60</v>
+      </c>
+      <c r="H15">
+        <v>14923.210069571334</v>
+      </c>
+      <c r="I15">
+        <v>14667.700099054911</v>
+      </c>
+      <c r="J15">
+        <v>16800.593377292033</v>
+      </c>
+      <c r="K15">
+        <v>15358.265439458381</v>
+      </c>
+      <c r="L15">
+        <v>16327.400777144165</v>
+      </c>
+      <c r="M15">
+        <v>15630.99119242193</v>
+      </c>
+      <c r="N15">
+        <v>15407.758745327439</v>
+      </c>
+      <c r="O15">
+        <v>15274.971184722855</v>
+      </c>
+      <c r="P15">
+        <v>16600.259866685319</v>
+      </c>
+      <c r="Q15">
+        <v>15711.178662660204</v>
+      </c>
+      <c r="R15">
+        <v>16242.126032764498</v>
+      </c>
+      <c r="S15">
+        <v>14193.353571432581</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>1100046</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>74.242169993392238</v>
+      </c>
+      <c r="I16">
+        <v>67.758706344275637</v>
+      </c>
+      <c r="J16">
+        <v>84.517327423272278</v>
+      </c>
+      <c r="K16">
+        <v>84.859378382739152</v>
+      </c>
+      <c r="L16">
+        <v>94.447424003013722</v>
+      </c>
+      <c r="M16">
+        <v>87.157197234559007</v>
+      </c>
+      <c r="N16">
+        <v>88.725628951930304</v>
+      </c>
+      <c r="O16">
+        <v>88.120746121642654</v>
+      </c>
+      <c r="P16">
+        <v>94.667969472024851</v>
+      </c>
+      <c r="Q16">
+        <v>85.830776814985782</v>
+      </c>
+      <c r="R16">
+        <v>80.560933029975132</v>
+      </c>
+      <c r="S16">
+        <v>65.920780309299104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>1100071</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+      <c r="H17">
+        <v>9864.7934812354342</v>
+      </c>
+      <c r="I17">
+        <v>9576.7013825908434</v>
+      </c>
+      <c r="J17">
+        <v>11010.020762187789</v>
+      </c>
+      <c r="K17">
+        <v>9533.7774783814548</v>
+      </c>
+      <c r="L17">
+        <v>10440.284553630872</v>
+      </c>
+      <c r="M17">
+        <v>9911.7576372880721</v>
+      </c>
+      <c r="N17">
+        <v>10144.890662710935</v>
+      </c>
+      <c r="O17">
+        <v>10472.002902701901</v>
+      </c>
+      <c r="P17">
+        <v>11256.705668099727</v>
+      </c>
+      <c r="Q17">
+        <v>10957.389661052648</v>
+      </c>
+      <c r="R17">
+        <v>10770.035158289507</v>
+      </c>
+      <c r="S17">
+        <v>9269.1310706548902</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>1101068</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18">
+        <v>7098.1285253110545</v>
+      </c>
+      <c r="I18">
+        <v>6209.4246012744779</v>
+      </c>
+      <c r="J18">
+        <v>7291.8418027748894</v>
+      </c>
+      <c r="K18">
+        <v>5975.0800106626684</v>
+      </c>
+      <c r="L18">
+        <v>6751.7065511594465</v>
+      </c>
+      <c r="M18">
+        <v>6172.4999749241224</v>
+      </c>
+      <c r="N18">
+        <v>5900.4058936450792</v>
+      </c>
+      <c r="O18">
+        <v>6266.6962290167457</v>
+      </c>
+      <c r="P18">
+        <v>7141.6487978034993</v>
+      </c>
+      <c r="Q18">
+        <v>6682.9567557638256</v>
+      </c>
+      <c r="R18">
+        <v>6602.1970353685165</v>
+      </c>
+      <c r="S18">
+        <v>5893.389808611174</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>1100047</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19">
+        <v>1527.9983054742574</v>
+      </c>
+      <c r="I19">
+        <v>1538.5055710031265</v>
+      </c>
+      <c r="J19">
+        <v>1693.6866765844886</v>
+      </c>
+      <c r="K19">
+        <v>1512.4122616974971</v>
+      </c>
+      <c r="L19">
+        <v>1630.6308285074456</v>
+      </c>
+      <c r="M19">
+        <v>1613.0879601541399</v>
+      </c>
+      <c r="N19">
+        <v>1723.5583736454953</v>
+      </c>
+      <c r="O19">
+        <v>1580.8907178584773</v>
+      </c>
+      <c r="P19">
+        <v>1687.3568483406598</v>
+      </c>
+      <c r="Q19">
+        <v>1620.4474545563248</v>
+      </c>
+      <c r="R19">
+        <v>1617.7655447241111</v>
+      </c>
+      <c r="S19">
+        <v>1409.2418562740604</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>1100659</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>60</v>
+      </c>
+      <c r="H20">
+        <v>1573.7373498489026</v>
+      </c>
+      <c r="I20">
+        <v>1503.1398206607887</v>
+      </c>
+      <c r="J20">
+        <v>1689.4737105181887</v>
+      </c>
+      <c r="K20">
+        <v>1569.1200494078739</v>
+      </c>
+      <c r="L20">
+        <v>1677.680360600157</v>
+      </c>
+      <c r="M20">
+        <v>1588.2254075762248</v>
+      </c>
+      <c r="N20">
+        <v>1614.9150272907798</v>
+      </c>
+      <c r="O20">
+        <v>1634.8342732079821</v>
+      </c>
+      <c r="P20">
+        <v>1825.7055301159603</v>
+      </c>
+      <c r="Q20">
+        <v>1724.1765481236603</v>
+      </c>
+      <c r="R20">
+        <v>1799.5601689678876</v>
+      </c>
+      <c r="S20">
+        <v>1538.1129399727786</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>1101020</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>5651.9589326550104</v>
+      </c>
+      <c r="I21">
+        <v>5237.1427620187324</v>
+      </c>
+      <c r="J21">
+        <v>6471.4228451035096</v>
+      </c>
+      <c r="K21">
+        <v>6269.2062961303172</v>
+      </c>
+      <c r="L21">
+        <v>7108.4794722581664</v>
+      </c>
+      <c r="M21">
+        <v>6822.3931954561749</v>
+      </c>
+      <c r="N21">
+        <v>6800.9623100152785</v>
+      </c>
+      <c r="O21">
+        <v>6841.7490313408916</v>
+      </c>
+      <c r="P21">
+        <v>7349.8864815439629</v>
+      </c>
+      <c r="Q21">
+        <v>6857.6288135186551</v>
+      </c>
+      <c r="R21">
+        <v>6763.9586829551581</v>
+      </c>
+      <c r="S21">
+        <v>6033.2152211769508</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22">
         <v>1100579</v>
       </c>
-      <c r="B2">
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23">
         <v>1102664</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>638.10421169219353</v>
+      </c>
+      <c r="I23">
+        <v>385.6019589240957</v>
+      </c>
+      <c r="J23">
+        <v>664.88001240149083</v>
+      </c>
+      <c r="K23">
+        <v>758.01620348146048</v>
+      </c>
+      <c r="L23">
+        <v>653.11712767577262</v>
+      </c>
+      <c r="M23">
+        <v>435.81632355880629</v>
+      </c>
+      <c r="N23">
+        <v>430.61523853154023</v>
+      </c>
+      <c r="O23">
+        <v>499.92056039958152</v>
+      </c>
+      <c r="P23">
+        <v>618.13297629945498</v>
+      </c>
+      <c r="Q23">
+        <v>476.55535516377591</v>
+      </c>
+      <c r="R23">
+        <v>404.41685313166261</v>
+      </c>
+      <c r="S23">
+        <v>389.65121933067559</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>1100050</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="H24">
+        <v>9135.3842016757717</v>
+      </c>
+      <c r="I24">
+        <v>9007.6589360716862</v>
+      </c>
+      <c r="J24">
+        <v>9926.0107051286595</v>
+      </c>
+      <c r="K24">
+        <v>8672.9421504819566</v>
+      </c>
+      <c r="L24">
+        <v>9341.3991203028236</v>
+      </c>
+      <c r="M24">
+        <v>9101.8868525324306</v>
+      </c>
+      <c r="N24">
+        <v>9186.483253787399</v>
+      </c>
+      <c r="O24">
+        <v>9240.2149555216183</v>
+      </c>
+      <c r="P24">
+        <v>9942.7278272146177</v>
+      </c>
+      <c r="Q24">
+        <v>9558.5955547155354</v>
+      </c>
+      <c r="R24">
+        <v>9619.3994628184282</v>
+      </c>
+      <c r="S24">
+        <v>8471.7317283473694</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>1100195</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>30</v>
+      </c>
+      <c r="H25">
+        <v>14482.717465387148</v>
+      </c>
+      <c r="I25">
+        <v>13428.803116430148</v>
+      </c>
+      <c r="J25">
+        <v>16557.732542399419</v>
+      </c>
+      <c r="K25">
+        <v>15332.284058061465</v>
+      </c>
+      <c r="L25">
+        <v>16469.586819943746</v>
+      </c>
+      <c r="M25">
+        <v>16283.256464761196</v>
+      </c>
+      <c r="N25">
+        <v>16209.121272131117</v>
+      </c>
+      <c r="O25">
+        <v>16523.516857139646</v>
+      </c>
+      <c r="P25">
+        <v>17727.501205661774</v>
+      </c>
+      <c r="Q25">
+        <v>16752.531866030324</v>
+      </c>
+      <c r="R25">
+        <v>16698.693724582139</v>
+      </c>
+      <c r="S25">
+        <v>15489.362989716536</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>1100052</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>60</v>
+      </c>
+      <c r="H26">
+        <v>7237.4699840318117</v>
+      </c>
+      <c r="I26">
+        <v>7152.2012072405905</v>
+      </c>
+      <c r="J26">
+        <v>8452.3594489131228</v>
+      </c>
+      <c r="K26">
+        <v>6673.54053995701</v>
+      </c>
+      <c r="L26">
+        <v>6914.4994676815177</v>
+      </c>
+      <c r="M26">
+        <v>6736.4548840695652</v>
+      </c>
+      <c r="N26">
+        <v>7717.8613130552794</v>
+      </c>
+      <c r="O26">
+        <v>7690.6500122040898</v>
+      </c>
+      <c r="P26">
+        <v>9037.4334756540484</v>
+      </c>
+      <c r="Q26">
+        <v>8803.340469258148</v>
+      </c>
+      <c r="R26">
+        <v>9068.0495680327513</v>
+      </c>
+      <c r="S26">
+        <v>7243.2988834965308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>1101667</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>30</v>
+      </c>
+      <c r="H27">
+        <v>74482.464330655886</v>
+      </c>
+      <c r="I27">
+        <v>67740.584257858529</v>
+      </c>
+      <c r="J27">
+        <v>78241.585743237403</v>
+      </c>
+      <c r="K27">
+        <v>73329.866255641376</v>
+      </c>
+      <c r="L27">
+        <v>82968.465020421587</v>
+      </c>
+      <c r="M27">
+        <v>81796.107056530949</v>
+      </c>
+      <c r="N27">
+        <v>77680.504310487784</v>
+      </c>
+      <c r="O27">
+        <v>78143.676947064945</v>
+      </c>
+      <c r="P27">
+        <v>83454.568066846638</v>
+      </c>
+      <c r="Q27">
+        <v>80758.916719262168</v>
+      </c>
+      <c r="R27">
+        <v>80884.304163597335</v>
+      </c>
+      <c r="S27">
+        <v>74439.949663088672</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28">
+        <v>1100058</v>
+      </c>
+      <c r="D28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>30</v>
+      </c>
+      <c r="H28">
+        <v>33125.591775218454</v>
+      </c>
+      <c r="I28">
+        <v>30777.576244606335</v>
+      </c>
+      <c r="J28">
+        <v>37078.419827689941</v>
+      </c>
+      <c r="K28">
+        <v>35247.767705149206</v>
+      </c>
+      <c r="L28">
+        <v>37909.221413235005</v>
+      </c>
+      <c r="M28">
+        <v>37204.729360938014</v>
+      </c>
+      <c r="N28">
+        <v>36721.262433105687</v>
+      </c>
+      <c r="O28">
+        <v>37416.277067554554</v>
+      </c>
+      <c r="P28">
+        <v>41461.213505192398</v>
+      </c>
+      <c r="Q28">
+        <v>37977.580811612104</v>
+      </c>
+      <c r="R28">
+        <v>37598.260605685886</v>
+      </c>
+      <c r="S28">
+        <v>34103.509203486487</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>1100060</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29">
+        <v>60</v>
+      </c>
+      <c r="H29">
+        <v>5906.6171015425152</v>
+      </c>
+      <c r="I29">
+        <v>5893.9042925342173</v>
+      </c>
+      <c r="J29">
+        <v>6705.0902731148844</v>
+      </c>
+      <c r="K29">
+        <v>5993.4547381372786</v>
+      </c>
+      <c r="L29">
+        <v>6511.4407714495601</v>
+      </c>
+      <c r="M29">
+        <v>6332.1637363038853</v>
+      </c>
+      <c r="N29">
+        <v>6457.2028550328723</v>
+      </c>
+      <c r="O29">
+        <v>6643.3698081488874</v>
+      </c>
+      <c r="P29">
+        <v>7087.7653546306874</v>
+      </c>
+      <c r="Q29">
+        <v>6738.8753721299927</v>
+      </c>
+      <c r="R29">
+        <v>6926.0566551158872</v>
+      </c>
+      <c r="S29">
+        <v>5991.2885159389843</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30">
+        <v>1100687</v>
+      </c>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30">
+        <v>90</v>
+      </c>
+      <c r="H30">
+        <v>104728.4028807774</v>
+      </c>
+      <c r="I30">
+        <v>98723.090061385752</v>
+      </c>
+      <c r="J30">
+        <v>110112.68168311063</v>
+      </c>
+      <c r="K30">
+        <v>102086.53000766285</v>
+      </c>
+      <c r="L30">
+        <v>107156.36403197407</v>
+      </c>
+      <c r="M30">
+        <v>102844.34470499285</v>
+      </c>
+      <c r="N30">
+        <v>106837.04906937972</v>
+      </c>
+      <c r="O30">
+        <v>104642.94787213365</v>
+      </c>
+      <c r="P30">
+        <v>105613.05058872748</v>
+      </c>
+      <c r="Q30">
+        <v>104233.55317950658</v>
+      </c>
+      <c r="R30">
+        <v>99904.415369014125</v>
+      </c>
+      <c r="S30">
+        <v>94457.321483599851</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31">
+        <v>1100582</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>90</v>
+      </c>
+      <c r="H31">
+        <v>14830.83642833078</v>
+      </c>
+      <c r="I31">
+        <v>10611.484641873876</v>
+      </c>
+      <c r="J31">
+        <v>13961.276494012756</v>
+      </c>
+      <c r="K31">
+        <v>9948.7969269369169</v>
+      </c>
+      <c r="L31">
+        <v>13546.628830295351</v>
+      </c>
+      <c r="M31">
+        <v>13972.930203203237</v>
+      </c>
+      <c r="N31">
+        <v>13343.678482766829</v>
+      </c>
+      <c r="O31">
+        <v>13278.956349037129</v>
+      </c>
+      <c r="P31">
+        <v>15157.05999566098</v>
+      </c>
+      <c r="Q31">
+        <v>9710.3514513719656</v>
+      </c>
+      <c r="R31">
+        <v>12035.04168141716</v>
+      </c>
+      <c r="S31">
+        <v>11395.733305816013</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32">
+        <v>1102425</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32">
+        <v>60</v>
+      </c>
+      <c r="H32">
+        <v>6357.4178115960067</v>
+      </c>
+      <c r="I32">
+        <v>7117.5714087796123</v>
+      </c>
+      <c r="J32">
+        <v>7666.4522993946166</v>
+      </c>
+      <c r="K32">
+        <v>6379.6890538239149</v>
+      </c>
+      <c r="L32">
+        <v>6085.6708020701126</v>
+      </c>
+      <c r="M32">
+        <v>5722.8974189608753</v>
+      </c>
+      <c r="N32">
+        <v>22532.517061510043</v>
+      </c>
+      <c r="O32">
+        <v>24525.320410891905</v>
+      </c>
+      <c r="P32">
+        <v>29411.952157412394</v>
+      </c>
+      <c r="Q32">
+        <v>31425.39384108103</v>
+      </c>
+      <c r="R32">
+        <v>30388.408444302393</v>
+      </c>
+      <c r="S32">
+        <v>23512.028771945686</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33">
+        <v>1102037</v>
+      </c>
+      <c r="D33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33">
+        <v>90</v>
+      </c>
+      <c r="H33">
+        <v>22236.100352904486</v>
+      </c>
+      <c r="I33">
+        <v>22943.061463608214</v>
+      </c>
+      <c r="J33">
+        <v>24018.52579472696</v>
+      </c>
+      <c r="K33">
+        <v>23888.900004110514</v>
+      </c>
+      <c r="L33">
+        <v>22922.161424999722</v>
+      </c>
+      <c r="M33">
+        <v>8276.192095115799</v>
+      </c>
+      <c r="N33">
+        <v>25455.940329790283</v>
+      </c>
+      <c r="O33">
+        <v>8732.9355462831918</v>
+      </c>
+      <c r="P33">
+        <v>7703.5028549335484</v>
+      </c>
+      <c r="Q33">
+        <v>7584.1189579492284</v>
+      </c>
+      <c r="R33">
+        <v>9063.7180610584619</v>
+      </c>
+      <c r="S33">
+        <v>8381.7470304673952</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34">
+        <v>1100491</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+      <c r="H34">
+        <v>2126.4580858638433</v>
+      </c>
+      <c r="I34">
+        <v>1983.5529859219459</v>
+      </c>
+      <c r="J34">
+        <v>2387.8352118548637</v>
+      </c>
+      <c r="K34">
+        <v>2241.1586463167259</v>
+      </c>
+      <c r="L34">
+        <v>2444.6101020986534</v>
+      </c>
+      <c r="M34">
+        <v>2410.1652033008609</v>
+      </c>
+      <c r="N34">
+        <v>2361.154309145069</v>
+      </c>
+      <c r="O34">
+        <v>2413.9141100986217</v>
+      </c>
+      <c r="P34">
+        <v>2600.732753206536</v>
+      </c>
+      <c r="Q34">
+        <v>2484.5912442774847</v>
+      </c>
+      <c r="R34">
+        <v>2465.6246300881239</v>
+      </c>
+      <c r="S34">
+        <v>2252.5937926562415</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1100063</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35">
+        <v>60</v>
+      </c>
+      <c r="H35">
+        <v>20291.487600477118</v>
+      </c>
+      <c r="I35">
+        <v>20286.5958251093</v>
+      </c>
+      <c r="J35">
+        <v>23609.527609588709</v>
+      </c>
+      <c r="K35">
+        <v>20498.895833961305</v>
+      </c>
+      <c r="L35">
+        <v>22059.216427198357</v>
+      </c>
+      <c r="M35">
+        <v>21667.163306655155</v>
+      </c>
+      <c r="N35">
+        <v>22028.661911633419</v>
+      </c>
+      <c r="O35">
+        <v>22351.607822720736</v>
+      </c>
+      <c r="P35">
+        <v>23521.837851297354</v>
+      </c>
+      <c r="Q35">
+        <v>22747.512790595447</v>
+      </c>
+      <c r="R35">
+        <v>22671.768929672453</v>
+      </c>
+      <c r="S35">
+        <v>19797.188090507967</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>1100041</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
+        <v>30</v>
+      </c>
+      <c r="H36">
+        <v>43356.327925674377</v>
+      </c>
+      <c r="I36">
+        <v>40279.864255596258</v>
+      </c>
+      <c r="J36">
+        <v>49103.496929489134</v>
+      </c>
+      <c r="K36">
+        <v>46311.564458368674</v>
+      </c>
+      <c r="L36">
+        <v>49968.269808911806</v>
+      </c>
+      <c r="M36">
+        <v>48605.164746488626</v>
+      </c>
+      <c r="N36">
+        <v>48127.016977184343</v>
+      </c>
+      <c r="O36">
+        <v>49076.560844226857</v>
+      </c>
+      <c r="P36">
+        <v>53173.193686507024</v>
+      </c>
+      <c r="Q36">
+        <v>50117.997007139296</v>
+      </c>
+      <c r="R36">
+        <v>49914.97730906331</v>
+      </c>
+      <c r="S36">
+        <v>45026.825092328683</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>1100689</v>
+      </c>
+      <c r="D37" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37">
+        <v>60</v>
+      </c>
+      <c r="H37">
+        <v>178.00005541076177</v>
+      </c>
+      <c r="I37">
+        <v>188.58616102987338</v>
+      </c>
+      <c r="J37">
+        <v>415.59355357064828</v>
+      </c>
+      <c r="K37">
+        <v>226.65591806399061</v>
+      </c>
+      <c r="L37">
+        <v>256.09170560243928</v>
+      </c>
+      <c r="M37">
+        <v>265.6292655489259</v>
+      </c>
+      <c r="N37">
+        <v>384.78452466392605</v>
+      </c>
+      <c r="O37">
+        <v>463.20907346687886</v>
+      </c>
+      <c r="P37">
+        <v>519.89686369786784</v>
+      </c>
+      <c r="Q37">
+        <v>549.20311720859638</v>
+      </c>
+      <c r="R37">
+        <v>601.06832641925087</v>
+      </c>
+      <c r="S37">
+        <v>452.56996504777902</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38">
+        <v>1101065</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38">
+        <v>60</v>
+      </c>
+      <c r="H38">
+        <v>1387.833895720622</v>
+      </c>
+      <c r="I38">
+        <v>1381.6690970599359</v>
+      </c>
+      <c r="J38">
+        <v>2167.4429113330621</v>
+      </c>
+      <c r="K38">
+        <v>1691.2133426826092</v>
+      </c>
+      <c r="L38">
+        <v>1741.6926857405172</v>
+      </c>
+      <c r="M38">
+        <v>1688.5226667168167</v>
+      </c>
+      <c r="N38">
+        <v>2257.9912581212457</v>
+      </c>
+      <c r="O38">
+        <v>2473.002918703663</v>
+      </c>
+      <c r="P38">
+        <v>2860.2947376336424</v>
+      </c>
+      <c r="Q38">
+        <v>3083.8146823405027</v>
+      </c>
+      <c r="R38">
+        <v>3153.5974586378015</v>
+      </c>
+      <c r="S38">
+        <v>2323.7563463935048</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39">
+        <v>1101861</v>
+      </c>
+      <c r="D39" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39">
+        <v>60</v>
+      </c>
+      <c r="H39">
+        <v>1275.6576190005726</v>
+      </c>
+      <c r="I39">
+        <v>1147.3621742531416</v>
+      </c>
+      <c r="J39">
+        <v>1227.0867803954284</v>
+      </c>
+      <c r="K39">
+        <v>1351.5395060557287</v>
+      </c>
+      <c r="L39">
+        <v>1340.5707610955292</v>
+      </c>
+      <c r="M39">
+        <v>1499.0652521625311</v>
+      </c>
+      <c r="N39">
+        <v>1276.3257347272449</v>
+      </c>
+      <c r="O39">
+        <v>980.70183953035325</v>
+      </c>
+      <c r="P39">
+        <v>1273.7646443451481</v>
+      </c>
+      <c r="Q39">
+        <v>1132.5730776628054</v>
+      </c>
+      <c r="R39">
+        <v>1017.5057819092167</v>
+      </c>
+      <c r="S39">
+        <v>767.6102330449711</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>1102043</v>
+      </c>
+      <c r="D40" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40">
+        <v>90</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>1100703</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41">
+        <v>90</v>
+      </c>
+      <c r="H41">
+        <v>36.988758729112739</v>
+      </c>
+      <c r="I41">
+        <v>32.494321633866761</v>
+      </c>
+      <c r="J41">
+        <v>37.138260204219741</v>
+      </c>
+      <c r="K41">
+        <v>34.040382180267436</v>
+      </c>
+      <c r="L41">
+        <v>34.485008709222619</v>
+      </c>
+      <c r="M41">
+        <v>34.485369636501765</v>
+      </c>
+      <c r="N41">
+        <v>35.742811543751465</v>
+      </c>
+      <c r="O41">
+        <v>36.867372468380424</v>
+      </c>
+      <c r="P41">
+        <v>36.759713737090699</v>
+      </c>
+      <c r="Q41">
+        <v>35.867119831513548</v>
+      </c>
+      <c r="R41">
+        <v>36.3816644008186</v>
+      </c>
+      <c r="S41">
+        <v>33.636583260765619</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42">
+        <v>1101569</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42">
+        <v>30</v>
+      </c>
+      <c r="H42">
+        <v>5500</v>
+      </c>
+      <c r="I42">
+        <v>5500</v>
+      </c>
+      <c r="J42">
+        <v>5500</v>
+      </c>
+      <c r="K42">
+        <v>5500</v>
+      </c>
+      <c r="L42">
+        <v>5500</v>
+      </c>
+      <c r="M42">
+        <v>4500</v>
+      </c>
+      <c r="N42">
+        <v>4500</v>
+      </c>
+      <c r="O42">
+        <v>4500</v>
+      </c>
+      <c r="P42">
+        <v>4500</v>
+      </c>
+      <c r="Q42">
+        <v>4000</v>
+      </c>
+      <c r="R42">
+        <v>4000</v>
+      </c>
+      <c r="S42">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43">
+        <v>1100590</v>
+      </c>
+      <c r="D43" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43">
+        <v>90</v>
+      </c>
+      <c r="H43">
+        <v>1465</v>
+      </c>
+      <c r="I43">
+        <v>1465</v>
+      </c>
+      <c r="J43">
+        <v>1465</v>
+      </c>
+      <c r="K43">
+        <v>1465</v>
+      </c>
+      <c r="L43">
+        <v>1040</v>
+      </c>
+      <c r="M43">
+        <v>1040</v>
+      </c>
+      <c r="N43">
+        <v>1664</v>
+      </c>
+      <c r="O43">
+        <v>832</v>
+      </c>
+      <c r="P43">
+        <v>832</v>
+      </c>
+      <c r="Q43">
+        <v>832</v>
+      </c>
+      <c r="R43">
+        <v>832</v>
+      </c>
+      <c r="S43">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44">
+        <v>1102444</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44">
+        <v>30</v>
+      </c>
+      <c r="H44">
+        <v>7500</v>
+      </c>
+      <c r="I44">
+        <v>7500</v>
+      </c>
+      <c r="J44">
+        <v>7500</v>
+      </c>
+      <c r="K44">
+        <v>7500</v>
+      </c>
+      <c r="L44">
+        <v>7500</v>
+      </c>
+      <c r="M44">
+        <v>6500</v>
+      </c>
+      <c r="N44">
+        <v>6500</v>
+      </c>
+      <c r="O44">
+        <v>6500</v>
+      </c>
+      <c r="P44">
+        <v>6500</v>
+      </c>
+      <c r="Q44">
+        <v>5500</v>
+      </c>
+      <c r="R44">
+        <v>5500</v>
+      </c>
+      <c r="S44">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45">
+        <v>1102008</v>
+      </c>
+      <c r="D45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45">
+        <v>90</v>
+      </c>
+      <c r="H45">
+        <v>27545.104442789478</v>
+      </c>
+      <c r="I45">
+        <v>82737.119420246803</v>
+      </c>
+      <c r="J45">
+        <v>23047.104807748878</v>
+      </c>
+      <c r="K45">
+        <v>16808.431350178475</v>
+      </c>
+      <c r="L45">
+        <v>20397.807849633453</v>
+      </c>
+      <c r="M45">
+        <v>21788.232089886333</v>
+      </c>
+      <c r="N45">
+        <v>19464.979060331181</v>
+      </c>
+      <c r="O45">
+        <v>20420.478156464374</v>
+      </c>
+      <c r="P45">
+        <v>21774.424565732628</v>
+      </c>
+      <c r="Q45">
+        <v>6096.5169128425769</v>
+      </c>
+      <c r="R45">
+        <v>5730.7774642277745</v>
+      </c>
+      <c r="S45">
+        <v>5995.337232688219</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46">
+        <v>1101932</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46">
+        <v>60</v>
+      </c>
+      <c r="H46">
+        <v>144926.77523361304</v>
+      </c>
+      <c r="I46">
+        <v>130970.84486145111</v>
+      </c>
+      <c r="J46">
+        <v>168812.6717407261</v>
+      </c>
+      <c r="K46">
+        <v>142371.70395080236</v>
+      </c>
+      <c r="L46">
+        <v>144619.72994184375</v>
+      </c>
+      <c r="M46">
+        <v>142386.94815428468</v>
+      </c>
+      <c r="N46">
+        <v>148734.3910010937</v>
+      </c>
+      <c r="O46">
+        <v>139250.88955538603</v>
+      </c>
+      <c r="P46">
+        <v>161151.14985992928</v>
+      </c>
+      <c r="Q46">
+        <v>159765.79189157562</v>
+      </c>
+      <c r="R46">
+        <v>165153.2572544507</v>
+      </c>
+      <c r="S46">
+        <v>141894.67265633738</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47">
+        <v>1100040</v>
+      </c>
+      <c r="D47" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47">
+        <v>90</v>
+      </c>
+      <c r="H47">
+        <v>49.644627768183568</v>
+      </c>
+      <c r="I47">
+        <v>62.413170474921927</v>
+      </c>
+      <c r="J47">
+        <v>56.184035041051089</v>
+      </c>
+      <c r="K47">
+        <v>52.654970399810402</v>
+      </c>
+      <c r="L47">
+        <v>62.406315704833837</v>
+      </c>
+      <c r="M47">
+        <v>63.665102674119439</v>
+      </c>
+      <c r="N47">
+        <v>69.953168587926896</v>
+      </c>
+      <c r="O47">
+        <v>63.697099550916739</v>
+      </c>
+      <c r="P47">
+        <v>44.042475320002922</v>
+      </c>
+      <c r="Q47">
+        <v>45.744505653198324</v>
+      </c>
+      <c r="R47">
+        <v>62.390545951204174</v>
+      </c>
+      <c r="S47">
+        <v>51.252017223080202</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48">
+        <v>1102190</v>
+      </c>
+      <c r="D48" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48">
+        <v>90</v>
+      </c>
+      <c r="H48">
+        <v>5179.1656477041015</v>
+      </c>
+      <c r="I48">
+        <v>6106.9491321205105</v>
+      </c>
+      <c r="J48">
+        <v>6287.1702449572713</v>
+      </c>
+      <c r="K48">
+        <v>5645.3170473083328</v>
+      </c>
+      <c r="L48">
+        <v>2592.823178586048</v>
+      </c>
+      <c r="M48">
+        <v>2452.3272051250265</v>
+      </c>
+      <c r="N48">
+        <v>2312.5527451249809</v>
+      </c>
+      <c r="O48">
+        <v>2295.5670623884334</v>
+      </c>
+      <c r="P48">
+        <v>2342.4841202289917</v>
+      </c>
+      <c r="Q48">
+        <v>2385.946238811759</v>
+      </c>
+      <c r="R48">
+        <v>2446.62519241668</v>
+      </c>
+      <c r="S48">
+        <v>2037.9401771463934</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49">
+        <v>1101441</v>
+      </c>
+      <c r="D49" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>42</v>
+      </c>
+      <c r="G49">
+        <v>90</v>
+      </c>
+      <c r="H49">
+        <v>903.73995883174666</v>
+      </c>
+      <c r="I49">
+        <v>1247.3021712096333</v>
+      </c>
+      <c r="J49">
+        <v>1239.114157825167</v>
+      </c>
+      <c r="K49">
+        <v>1090.1680026195534</v>
+      </c>
+      <c r="L49">
+        <v>1300.5644029894952</v>
+      </c>
+      <c r="M49">
+        <v>1182.1783045033917</v>
+      </c>
+      <c r="N49">
+        <v>1154.3671762740917</v>
+      </c>
+      <c r="O49">
+        <v>1032.97654332763</v>
+      </c>
+      <c r="P49">
+        <v>1152.0586245051247</v>
+      </c>
+      <c r="Q49">
+        <v>1200.4695348870714</v>
+      </c>
+      <c r="R49">
+        <v>974.06514722951908</v>
+      </c>
+      <c r="S49">
+        <v>954.51907500513153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50">
         <v>1102325</v>
       </c>
-      <c r="B3">
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50">
+        <v>60</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51">
         <v>1102504</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1102043</v>
-      </c>
-      <c r="B4">
-        <v>1100703</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1102241</v>
-      </c>
-      <c r="B5">
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51">
+        <v>60</v>
+      </c>
+      <c r="H51">
+        <v>3877.5483146185688</v>
+      </c>
+      <c r="I51">
+        <v>4096.2612514662515</v>
+      </c>
+      <c r="J51">
+        <v>8586.3196445256563</v>
+      </c>
+      <c r="K51">
+        <v>4682.7967977371645</v>
+      </c>
+      <c r="L51">
+        <v>5290.9512761258684</v>
+      </c>
+      <c r="M51">
+        <v>5688.0008636995053</v>
+      </c>
+      <c r="N51">
+        <v>7949.7934812641315</v>
+      </c>
+      <c r="O51">
+        <v>9570.0742537024944</v>
+      </c>
+      <c r="P51">
+        <v>14241.265391493684</v>
+      </c>
+      <c r="Q51">
+        <v>14846.743647988924</v>
+      </c>
+      <c r="R51">
+        <v>14918.298442058107</v>
+      </c>
+      <c r="S51">
+        <v>9350.266259005999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52">
+        <v>1100690</v>
+      </c>
+      <c r="D52" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52">
+        <v>90</v>
+      </c>
+      <c r="H52">
+        <v>4711.9606769135635</v>
+      </c>
+      <c r="I52">
+        <v>4404.0960048536817</v>
+      </c>
+      <c r="J52">
+        <v>5921.5417823548205</v>
+      </c>
+      <c r="K52">
+        <v>6096.2400151022212</v>
+      </c>
+      <c r="L52">
+        <v>4749.4098854445838</v>
+      </c>
+      <c r="M52">
+        <v>4882.6576263745937</v>
+      </c>
+      <c r="N52">
+        <v>6043.0712616003912</v>
+      </c>
+      <c r="O52">
+        <v>7258.1529621023446</v>
+      </c>
+      <c r="P52">
+        <v>9252.4689172073558</v>
+      </c>
+      <c r="Q52">
+        <v>10894.204977794558</v>
+      </c>
+      <c r="R52">
+        <v>10590.822212576848</v>
+      </c>
+      <c r="S52">
+        <v>8967.8661353562147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53">
+        <v>1100175</v>
+      </c>
+      <c r="D53" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" t="s">
+        <v>66</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>30</v>
+      </c>
+      <c r="H53">
+        <v>140388.17851948258</v>
+      </c>
+      <c r="I53">
+        <v>124812.7318693804</v>
+      </c>
+      <c r="J53">
+        <v>144026.08460816299</v>
+      </c>
+      <c r="K53">
+        <v>136482.62169164195</v>
+      </c>
+      <c r="L53">
+        <v>147441.11063561987</v>
+      </c>
+      <c r="M53">
+        <v>149979.15031297252</v>
+      </c>
+      <c r="N53">
+        <v>148874.54794429152</v>
+      </c>
+      <c r="O53">
+        <v>152403.76066363006</v>
+      </c>
+      <c r="P53">
+        <v>159926.36450141258</v>
+      </c>
+      <c r="Q53">
+        <v>159504.52526457657</v>
+      </c>
+      <c r="R53">
+        <v>154170.32253167097</v>
+      </c>
+      <c r="S53">
+        <v>146861.67172792478</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54">
+        <v>1100174</v>
+      </c>
+      <c r="D54" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>30</v>
+      </c>
+      <c r="H54">
+        <v>209544.43749861018</v>
+      </c>
+      <c r="I54">
+        <v>183238.49053493908</v>
+      </c>
+      <c r="J54">
+        <v>224729.95185771043</v>
+      </c>
+      <c r="K54">
+        <v>225944.0631422986</v>
+      </c>
+      <c r="L54">
+        <v>244199.80895724602</v>
+      </c>
+      <c r="M54">
+        <v>238243.63030005738</v>
+      </c>
+      <c r="N54">
+        <v>235124.86385114543</v>
+      </c>
+      <c r="O54">
+        <v>229564.18336114919</v>
+      </c>
+      <c r="P54">
+        <v>243446.92792250463</v>
+      </c>
+      <c r="Q54">
+        <v>236682.67743989365</v>
+      </c>
+      <c r="R54">
+        <v>223511.68072741487</v>
+      </c>
+      <c r="S54">
+        <v>199441.41384510405</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>1100172</v>
+      </c>
+      <c r="D55" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>30</v>
+      </c>
+      <c r="H55">
+        <v>263177.09835760377</v>
+      </c>
+      <c r="I55">
+        <v>243160.22946337349</v>
+      </c>
+      <c r="J55">
+        <v>294187.50699994987</v>
+      </c>
+      <c r="K55">
+        <v>273831.74869505601</v>
+      </c>
+      <c r="L55">
+        <v>295852.35701451887</v>
+      </c>
+      <c r="M55">
+        <v>294163.16136667214</v>
+      </c>
+      <c r="N55">
+        <v>289357.45985516929</v>
+      </c>
+      <c r="O55">
+        <v>294559.52414752648</v>
+      </c>
+      <c r="P55">
+        <v>314957.65157110442</v>
+      </c>
+      <c r="Q55">
+        <v>302820.33546382486</v>
+      </c>
+      <c r="R55">
+        <v>306120.55984818575</v>
+      </c>
+      <c r="S55">
+        <v>279070.49553459033</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56">
+        <v>1100219</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" t="s">
+        <v>66</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56">
+        <v>30</v>
+      </c>
+      <c r="H56">
+        <v>73106.9291888273</v>
+      </c>
+      <c r="I56">
+        <v>75727.33041036193</v>
+      </c>
+      <c r="J56">
+        <v>92963.92375831386</v>
+      </c>
+      <c r="K56">
+        <v>85786.512342732152</v>
+      </c>
+      <c r="L56">
+        <v>94033.606225218129</v>
+      </c>
+      <c r="M56">
+        <v>90482.28016453411</v>
+      </c>
+      <c r="N56">
+        <v>89361.771661461578</v>
+      </c>
+      <c r="O56">
+        <v>92526.383290828395</v>
+      </c>
+      <c r="P56">
+        <v>102054.31324441798</v>
+      </c>
+      <c r="Q56">
+        <v>83821.711998868253</v>
+      </c>
+      <c r="R56">
+        <v>90591.179087540222</v>
+      </c>
+      <c r="S56">
+        <v>86044.350941170545</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>1100173</v>
+      </c>
+      <c r="D57" t="s">
+        <v>70</v>
+      </c>
+      <c r="E57" t="s">
+        <v>66</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57">
+        <v>30</v>
+      </c>
+      <c r="H57">
+        <v>233917.46238781544</v>
+      </c>
+      <c r="I57">
+        <v>214909.95057734192</v>
+      </c>
+      <c r="J57">
+        <v>261847.09655823585</v>
+      </c>
+      <c r="K57">
+        <v>245347.92648007724</v>
+      </c>
+      <c r="L57">
+        <v>263842.91459128686</v>
+      </c>
+      <c r="M57">
+        <v>261613.37978433265</v>
+      </c>
+      <c r="N57">
+        <v>257761.43794650247</v>
+      </c>
+      <c r="O57">
+        <v>263831.43875265983</v>
+      </c>
+      <c r="P57">
+        <v>281262.4849915572</v>
+      </c>
+      <c r="Q57">
+        <v>267690.46714210336</v>
+      </c>
+      <c r="R57">
+        <v>263432.42047218885</v>
+      </c>
+      <c r="S57">
+        <v>241406.81341493499</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>1100287</v>
+      </c>
+      <c r="D58" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" t="s">
+        <v>72</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58">
+        <v>30</v>
+      </c>
+      <c r="H58">
+        <v>24594.056771740317</v>
+      </c>
+      <c r="I58">
+        <v>24591.781188908859</v>
+      </c>
+      <c r="J58">
+        <v>31150.339492774001</v>
+      </c>
+      <c r="K58">
+        <v>30411.067193656552</v>
+      </c>
+      <c r="L58">
+        <v>33682.648035552171</v>
+      </c>
+      <c r="M58">
+        <v>31966.267014008372</v>
+      </c>
+      <c r="N58">
+        <v>33429.478438998529</v>
+      </c>
+      <c r="O58">
+        <v>34721.582148724505</v>
+      </c>
+      <c r="P58">
+        <v>38236.279631668658</v>
+      </c>
+      <c r="Q58">
+        <v>35014.532064956176</v>
+      </c>
+      <c r="R58">
+        <v>35212.821346958815</v>
+      </c>
+      <c r="S58">
+        <v>28974.396341034855</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>1100098</v>
+      </c>
+      <c r="D59" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59">
+        <v>60</v>
+      </c>
+      <c r="H59">
+        <v>166868.90275419966</v>
+      </c>
+      <c r="I59">
+        <v>161356.14696587023</v>
+      </c>
+      <c r="J59">
+        <v>184686.84095882217</v>
+      </c>
+      <c r="K59">
+        <v>161869.46780870581</v>
+      </c>
+      <c r="L59">
+        <v>175046.34561188729</v>
+      </c>
+      <c r="M59">
+        <v>168632.8671234987</v>
+      </c>
+      <c r="N59">
+        <v>171108.72618178936</v>
+      </c>
+      <c r="O59">
+        <v>173665.02652192049</v>
+      </c>
+      <c r="P59">
+        <v>186398.94534017573</v>
+      </c>
+      <c r="Q59">
+        <v>178691.98727227814</v>
+      </c>
+      <c r="R59">
+        <v>179678.33292825602</v>
+      </c>
+      <c r="S59">
+        <v>158693.0747505801</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>1100100</v>
+      </c>
+      <c r="D60" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60">
+        <v>60</v>
+      </c>
+      <c r="H60">
+        <v>94718.254364071196</v>
+      </c>
+      <c r="I60">
+        <v>98762.225771356592</v>
+      </c>
+      <c r="J60">
+        <v>79845.158861769232</v>
+      </c>
+      <c r="K60">
+        <v>68940.754951388371</v>
+      </c>
+      <c r="L60">
+        <v>72655.004513853593</v>
+      </c>
+      <c r="M60">
+        <v>70341.378614070869</v>
+      </c>
+      <c r="N60">
+        <v>72571.611165990558</v>
+      </c>
+      <c r="O60">
+        <v>71534.658868837083</v>
+      </c>
+      <c r="P60">
+        <v>73144.887901649752</v>
+      </c>
+      <c r="Q60">
+        <v>69465.203316324551</v>
+      </c>
+      <c r="R60">
+        <v>70229.909576444188</v>
+      </c>
+      <c r="S60">
+        <v>61180.92706490952</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>1101287</v>
+      </c>
+      <c r="D61" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61">
+        <v>30</v>
+      </c>
+      <c r="H61">
+        <v>34530.133937508937</v>
+      </c>
+      <c r="I61">
+        <v>29565.026952621833</v>
+      </c>
+      <c r="J61">
+        <v>34431.78898628708</v>
+      </c>
+      <c r="K61">
+        <v>36846.568241782028</v>
+      </c>
+      <c r="L61">
+        <v>41193.047530312891</v>
+      </c>
+      <c r="M61">
+        <v>46153.975628900778</v>
+      </c>
+      <c r="N61">
+        <v>45933.93475234088</v>
+      </c>
+      <c r="O61">
+        <v>46339.525802324344</v>
+      </c>
+      <c r="P61">
+        <v>45437.490096833215</v>
+      </c>
+      <c r="Q61">
+        <v>44087.149273974006</v>
+      </c>
+      <c r="R61">
+        <v>42459.237604087881</v>
+      </c>
+      <c r="S61">
+        <v>37140.027373847617</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>1100765</v>
+      </c>
+      <c r="D62" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" t="s">
+        <v>72</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62">
+        <v>30</v>
+      </c>
+      <c r="H62">
+        <v>228859.80488137028</v>
+      </c>
+      <c r="I62">
+        <v>198575.0498025431</v>
+      </c>
+      <c r="J62">
+        <v>237362.35713935265</v>
+      </c>
+      <c r="K62">
+        <v>232188.43667808975</v>
+      </c>
+      <c r="L62">
+        <v>247578.11075974774</v>
+      </c>
+      <c r="M62">
+        <v>238723.70059021513</v>
+      </c>
+      <c r="N62">
+        <v>238055.2677557696</v>
+      </c>
+      <c r="O62">
+        <v>234169.29187375668</v>
+      </c>
+      <c r="P62">
+        <v>252575.70873576018</v>
+      </c>
+      <c r="Q62">
+        <v>244826.0913364467</v>
+      </c>
+      <c r="R62">
+        <v>239125.67660367905</v>
+      </c>
+      <c r="S62">
+        <v>219194.30579948213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>1100838</v>
+      </c>
+      <c r="D63" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63">
+        <v>90</v>
+      </c>
+      <c r="H63">
+        <v>32311.764311598363</v>
+      </c>
+      <c r="I63">
+        <v>24785.232690404013</v>
+      </c>
+      <c r="J63">
+        <v>26478.231056942786</v>
+      </c>
+      <c r="K63">
+        <v>21305.493183028961</v>
+      </c>
+      <c r="L63">
+        <v>18011.007112032388</v>
+      </c>
+      <c r="M63">
+        <v>19801.511352820649</v>
+      </c>
+      <c r="N63">
+        <v>20765.429692761787</v>
+      </c>
+      <c r="O63">
+        <v>21189.631510929034</v>
+      </c>
+      <c r="P63">
+        <v>17655.061152667571</v>
+      </c>
+      <c r="Q63">
+        <v>19583.182076492107</v>
+      </c>
+      <c r="R63">
+        <v>17298.026252678359</v>
+      </c>
+      <c r="S63">
+        <v>14552.737262082092</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>1100724</v>
+      </c>
+      <c r="D64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" t="s">
+        <v>72</v>
+      </c>
+      <c r="F64" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64">
+        <v>90</v>
+      </c>
+      <c r="H64">
+        <v>52883.771590796197</v>
+      </c>
+      <c r="I64">
+        <v>53683.924792259837</v>
+      </c>
+      <c r="J64">
+        <v>55401.077352984597</v>
+      </c>
+      <c r="K64">
+        <v>48671.599365016918</v>
+      </c>
+      <c r="L64">
+        <v>52698.116105081557</v>
+      </c>
+      <c r="M64">
+        <v>50875.492926274812</v>
+      </c>
+      <c r="N64">
+        <v>53988.648683746331</v>
+      </c>
+      <c r="O64">
+        <v>55436.665369328708</v>
+      </c>
+      <c r="P64">
+        <v>58402.064598416488</v>
+      </c>
+      <c r="Q64">
+        <v>58634.486245008178</v>
+      </c>
+      <c r="R64">
+        <v>60985.785248277032</v>
+      </c>
+      <c r="S64">
+        <v>57028.205253216765</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>1102038</v>
+      </c>
+      <c r="D65" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65">
+        <v>60</v>
+      </c>
+      <c r="H65">
+        <v>224113.15369711522</v>
+      </c>
+      <c r="I65">
+        <v>220791.95369206546</v>
+      </c>
+      <c r="J65">
+        <v>253234.56633831211</v>
+      </c>
+      <c r="K65">
+        <v>224171.52588287395</v>
+      </c>
+      <c r="L65">
+        <v>237860.57966354175</v>
+      </c>
+      <c r="M65">
+        <v>225494.84544503974</v>
+      </c>
+      <c r="N65">
+        <v>229649.84605148903</v>
+      </c>
+      <c r="O65">
+        <v>229411.96506883026</v>
+      </c>
+      <c r="P65">
+        <v>258828.12727253573</v>
+      </c>
+      <c r="Q65">
+        <v>245848.73103025727</v>
+      </c>
+      <c r="R65">
+        <v>253809.93450213471</v>
+      </c>
+      <c r="S65">
+        <v>214306.92791358673</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>1101828</v>
+      </c>
+      <c r="D66" t="s">
+        <v>80</v>
+      </c>
+      <c r="E66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66">
+        <v>90</v>
+      </c>
+      <c r="H66">
+        <v>142516.07412527365</v>
+      </c>
+      <c r="I66">
+        <v>134944.18848276403</v>
+      </c>
+      <c r="J66">
+        <v>180352.13235761764</v>
+      </c>
+      <c r="K66">
+        <v>162696.49666949981</v>
+      </c>
+      <c r="L66">
+        <v>167871.31187330151</v>
+      </c>
+      <c r="M66">
+        <v>153671.96218114602</v>
+      </c>
+      <c r="N66">
+        <v>163447.46960687803</v>
+      </c>
+      <c r="O66">
+        <v>163886.25363590865</v>
+      </c>
+      <c r="P66">
+        <v>167796.84088280934</v>
+      </c>
+      <c r="Q66">
+        <v>166664.42868185305</v>
+      </c>
+      <c r="R66">
+        <v>165706.5450316715</v>
+      </c>
+      <c r="S66">
+        <v>152251.56455254077</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>1100310</v>
+      </c>
+      <c r="D67" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" t="s">
+        <v>72</v>
+      </c>
+      <c r="F67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67">
+        <v>60</v>
+      </c>
+      <c r="H67">
+        <v>93154.156342190006</v>
+      </c>
+      <c r="I67">
+        <v>101740.49987887392</v>
+      </c>
+      <c r="J67">
+        <v>110501.00647770859</v>
+      </c>
+      <c r="K67">
+        <v>99294.804415205246</v>
+      </c>
+      <c r="L67">
+        <v>107693.89959838284</v>
+      </c>
+      <c r="M67">
+        <v>106623.5200149298</v>
+      </c>
+      <c r="N67">
+        <v>107405.77226273775</v>
+      </c>
+      <c r="O67">
+        <v>112558.67567098074</v>
+      </c>
+      <c r="P67">
+        <v>116075.23466320315</v>
+      </c>
+      <c r="Q67">
+        <v>110356.76749524838</v>
+      </c>
+      <c r="R67">
+        <v>109636.06156598666</v>
+      </c>
+      <c r="S67">
+        <v>95330.610133046532</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68">
+        <v>1102065</v>
+      </c>
+      <c r="D68" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" t="s">
+        <v>72</v>
+      </c>
+      <c r="F68" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68">
+        <v>60</v>
+      </c>
+      <c r="H68">
+        <v>22932.305145358572</v>
+      </c>
+      <c r="I68">
+        <v>22383.146692672432</v>
+      </c>
+      <c r="J68">
+        <v>27166.147600387831</v>
+      </c>
+      <c r="K68">
+        <v>25616.096055170692</v>
+      </c>
+      <c r="L68">
+        <v>24542.579210459106</v>
+      </c>
+      <c r="M68">
+        <v>28721.031716877795</v>
+      </c>
+      <c r="N68">
+        <v>22740.393225321877</v>
+      </c>
+      <c r="O68">
+        <v>18566.295168163735</v>
+      </c>
+      <c r="P68">
+        <v>26289.647134887276</v>
+      </c>
+      <c r="Q68">
+        <v>20488.672377141815</v>
+      </c>
+      <c r="R68">
+        <v>21285.193799867731</v>
+      </c>
+      <c r="S68">
+        <v>17057.706426070166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69">
+        <v>1102322</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69">
+        <v>60</v>
+      </c>
+      <c r="H69">
+        <v>4976.8097831002642</v>
+      </c>
+      <c r="I69">
+        <v>5107.9249068561412</v>
+      </c>
+      <c r="J69">
+        <v>11036.34012731224</v>
+      </c>
+      <c r="K69">
+        <v>6018.986055319514</v>
+      </c>
+      <c r="L69">
+        <v>6800.6713350802229</v>
+      </c>
+      <c r="M69">
+        <v>7278.9470527849289</v>
+      </c>
+      <c r="N69">
+        <v>10293.187586000073</v>
+      </c>
+      <c r="O69">
+        <v>12300.799280729483</v>
+      </c>
+      <c r="P69">
+        <v>18806.178102609043</v>
+      </c>
+      <c r="Q69">
+        <v>19584.423527310166</v>
+      </c>
+      <c r="R69">
+        <v>18461.735770739098</v>
+      </c>
+      <c r="S69">
+        <v>12018.271271919601</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70">
+        <v>1102082</v>
+      </c>
+      <c r="D70" t="s">
+        <v>84</v>
+      </c>
+      <c r="E70" t="s">
+        <v>72</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70">
+        <v>60</v>
+      </c>
+      <c r="H70">
+        <v>51599.94390742523</v>
+      </c>
+      <c r="I70">
+        <v>48014.162089227808</v>
+      </c>
+      <c r="J70">
+        <v>62156.928855142367</v>
+      </c>
+      <c r="K70">
+        <v>51272.126911590211</v>
+      </c>
+      <c r="L70">
+        <v>51063.856129426975</v>
+      </c>
+      <c r="M70">
+        <v>48786.297757008753</v>
+      </c>
+      <c r="N70">
+        <v>47725.876942060851</v>
+      </c>
+      <c r="O70">
+        <v>43598.767739352013</v>
+      </c>
+      <c r="P70">
+        <v>49599.486891162211</v>
+      </c>
+      <c r="Q70">
+        <v>48710.799288578281</v>
+      </c>
+      <c r="R70">
+        <v>49599.54558055332</v>
+      </c>
+      <c r="S70">
+        <v>48384.821567726816</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71">
+        <v>1102349</v>
+      </c>
+      <c r="D71" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71">
+        <v>60</v>
+      </c>
+      <c r="H71">
+        <v>4869.0544936228307</v>
+      </c>
+      <c r="I71">
+        <v>2903.8693146670498</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72">
+        <v>1102523</v>
+      </c>
+      <c r="D72" t="s">
+        <v>86</v>
+      </c>
+      <c r="E72" t="s">
+        <v>72</v>
+      </c>
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72">
+        <v>60</v>
+      </c>
+      <c r="H72">
+        <v>2701.8526149826453</v>
+      </c>
+      <c r="I72">
+        <v>2862.5385040037213</v>
+      </c>
+      <c r="J72">
+        <v>6308.4060085594274</v>
+      </c>
+      <c r="K72">
+        <v>3440.4709676214175</v>
+      </c>
+      <c r="L72">
+        <v>3887.2846811133954</v>
+      </c>
+      <c r="M72">
+        <v>4032.0578614394071</v>
+      </c>
+      <c r="N72">
+        <v>5840.7474960459303</v>
+      </c>
+      <c r="O72">
+        <v>7031.1747551708913</v>
+      </c>
+      <c r="P72">
+        <v>7891.6539263049453</v>
+      </c>
+      <c r="Q72">
+        <v>8336.5014080501551</v>
+      </c>
+      <c r="R72">
+        <v>9123.7773284983905</v>
+      </c>
+      <c r="S72">
+        <v>6869.6808751524777</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73">
+        <v>1100520</v>
+      </c>
+      <c r="D73" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" t="s">
+        <v>88</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73">
+        <v>30</v>
+      </c>
+      <c r="H73">
+        <v>330117.91400737502</v>
+      </c>
+      <c r="I73">
+        <v>535435.52510555519</v>
+      </c>
+      <c r="J73">
+        <v>571192.22099390836</v>
+      </c>
+      <c r="K73">
+        <v>529314.58866677794</v>
+      </c>
+      <c r="L73">
+        <v>657433.15534261905</v>
+      </c>
+      <c r="M73">
+        <v>671129.41983817599</v>
+      </c>
+      <c r="N73">
+        <v>650887.90063297621</v>
+      </c>
+      <c r="O73">
+        <v>665053.59181840601</v>
+      </c>
+      <c r="P73">
+        <v>712929.86998276529</v>
+      </c>
+      <c r="Q73">
+        <v>691622.32354550378</v>
+      </c>
+      <c r="R73">
+        <v>676786.1078727782</v>
+      </c>
+      <c r="S73">
+        <v>622855.53540035198</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74">
+        <v>1100946</v>
+      </c>
+      <c r="D74" t="s">
+        <v>89</v>
+      </c>
+      <c r="E74" t="s">
+        <v>88</v>
+      </c>
+      <c r="F74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74">
+        <v>30</v>
+      </c>
+      <c r="H74">
+        <v>18604.25521191665</v>
+      </c>
+      <c r="I74">
+        <v>13551.609769242403</v>
+      </c>
+      <c r="J74">
+        <v>3698.2523761774055</v>
+      </c>
+      <c r="K74">
+        <v>3555.5573940440013</v>
+      </c>
+      <c r="L74">
+        <v>3754.3483614197226</v>
+      </c>
+      <c r="M74">
+        <v>3713.8436993463856</v>
+      </c>
+      <c r="N74">
+        <v>3723.8662215698673</v>
+      </c>
+      <c r="O74">
+        <v>3696.2285103200752</v>
+      </c>
+      <c r="P74">
+        <v>3819.8695944854935</v>
+      </c>
+      <c r="Q74">
+        <v>4066.0815626740437</v>
+      </c>
+      <c r="R74">
+        <v>3653.2232184219374</v>
+      </c>
+      <c r="S74">
+        <v>15066.00281672721</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75">
+        <v>1100088</v>
+      </c>
+      <c r="D75" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" t="s">
+        <v>88</v>
+      </c>
+      <c r="F75" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75">
+        <v>90</v>
+      </c>
+      <c r="H75">
+        <v>225226.545337316</v>
+      </c>
+      <c r="I75">
+        <v>85937.428194601947</v>
+      </c>
+      <c r="J75">
+        <v>122617.14397701884</v>
+      </c>
+      <c r="K75">
+        <v>118727.96145976223</v>
+      </c>
+      <c r="L75">
+        <v>116131.30800384683</v>
+      </c>
+      <c r="M75">
+        <v>114199.70295650889</v>
+      </c>
+      <c r="N75">
+        <v>85295.493724857442</v>
+      </c>
+      <c r="O75">
+        <v>87481.788857426101</v>
+      </c>
+      <c r="P75">
+        <v>86382.805146295417</v>
+      </c>
+      <c r="Q75">
+        <v>84697.02493872965</v>
+      </c>
+      <c r="R75">
+        <v>85970.062106608762</v>
+      </c>
+      <c r="S75">
+        <v>76869.676201000068</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76">
         <v>1100114</v>
       </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1102260</v>
-      </c>
-      <c r="B6">
-        <v>1100114</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1102037</v>
-      </c>
-      <c r="B7">
-        <v>1102425</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2</v>
+      <c r="D76" t="s">
+        <v>91</v>
+      </c>
+      <c r="E76" t="s">
+        <v>88</v>
+      </c>
+      <c r="F76" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76">
+        <v>90</v>
+      </c>
+      <c r="H76">
+        <v>319455.5666827099</v>
+      </c>
+      <c r="I76">
+        <v>321038.98889346578</v>
+      </c>
+      <c r="J76">
+        <v>434093.76890268043</v>
+      </c>
+      <c r="K76">
+        <v>399980.61709357193</v>
+      </c>
+      <c r="L76">
+        <v>414584.81220700132</v>
+      </c>
+      <c r="M76">
+        <v>403162.93232573936</v>
+      </c>
+      <c r="N76">
+        <v>359987.70659812202</v>
+      </c>
+      <c r="O76">
+        <v>247574.37643257302</v>
+      </c>
+      <c r="P76">
+        <v>269898.44023506402</v>
+      </c>
+      <c r="Q76">
+        <v>267665.23767218873</v>
+      </c>
+      <c r="R76">
+        <v>260314.535511667</v>
+      </c>
+      <c r="S76">
+        <v>190245.35940326587</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77">
+        <v>1101000</v>
+      </c>
+      <c r="D77" t="s">
+        <v>92</v>
+      </c>
+      <c r="E77" t="s">
+        <v>93</v>
+      </c>
+      <c r="F77" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77">
+        <v>30</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78">
+        <v>1100991</v>
+      </c>
+      <c r="D78" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" t="s">
+        <v>93</v>
+      </c>
+      <c r="F78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78">
+        <v>60</v>
+      </c>
+      <c r="H78">
+        <v>1278.8595617999995</v>
+      </c>
+      <c r="I78">
+        <v>1260.2449587600001</v>
+      </c>
+      <c r="J78">
+        <v>1470.7655045999993</v>
+      </c>
+      <c r="K78">
+        <v>1303.0653784000001</v>
+      </c>
+      <c r="L78">
+        <v>1394.5175978499988</v>
+      </c>
+      <c r="M78">
+        <v>1349.1177611499998</v>
+      </c>
+      <c r="N78">
+        <v>1381.6221916000006</v>
+      </c>
+      <c r="O78">
+        <v>1383.5290180000006</v>
+      </c>
+      <c r="P78">
+        <v>1485.0583879500007</v>
+      </c>
+      <c r="Q78">
+        <v>1413.341862799999</v>
+      </c>
+      <c r="R78">
+        <v>1437.4341257499993</v>
+      </c>
+      <c r="S78">
+        <v>1257.8192087499992</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>1100356</v>
+      </c>
+      <c r="D79" t="s">
+        <v>95</v>
+      </c>
+      <c r="E79" t="s">
+        <v>93</v>
+      </c>
+      <c r="F79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79">
+        <v>60</v>
+      </c>
+      <c r="H79">
+        <v>35867.759261769432</v>
+      </c>
+      <c r="I79">
+        <v>35589.710395833223</v>
+      </c>
+      <c r="J79">
+        <v>41899.378510683156</v>
+      </c>
+      <c r="K79">
+        <v>36838.566196982036</v>
+      </c>
+      <c r="L79">
+        <v>38768.107638636233</v>
+      </c>
+      <c r="M79">
+        <v>37939.105237711403</v>
+      </c>
+      <c r="N79">
+        <v>38637.605455976402</v>
+      </c>
+      <c r="O79">
+        <v>19889.037313837096</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>1100711</v>
+      </c>
+      <c r="D80" t="s">
+        <v>96</v>
+      </c>
+      <c r="E80" t="s">
+        <v>93</v>
+      </c>
+      <c r="F80" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80">
+        <v>90</v>
+      </c>
+      <c r="H80">
+        <v>17.393687670240002</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>8.3022437295000007</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81">
+        <v>1102410</v>
+      </c>
+      <c r="D81" t="s">
+        <v>97</v>
+      </c>
+      <c r="E81" t="s">
+        <v>93</v>
+      </c>
+      <c r="F81" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81">
+        <v>60</v>
+      </c>
+      <c r="H81">
+        <v>5121.506435890321</v>
+      </c>
+      <c r="I81">
+        <v>3646.2261158114402</v>
+      </c>
+      <c r="J81">
+        <v>3274.7236812933747</v>
+      </c>
+      <c r="K81">
+        <v>4853.5990548342743</v>
+      </c>
+      <c r="L81">
+        <v>5216.6670421337994</v>
+      </c>
+      <c r="M81">
+        <v>3261.955612221675</v>
+      </c>
+      <c r="N81">
+        <v>3438.0385698919495</v>
+      </c>
+      <c r="O81">
+        <v>3572.4798008675994</v>
+      </c>
+      <c r="P81">
+        <v>3080.1524738559756</v>
+      </c>
+      <c r="Q81">
+        <v>3095.1994525665741</v>
+      </c>
+      <c r="R81">
+        <v>2809.6391746163249</v>
+      </c>
+      <c r="S81">
+        <v>2662.0099619364</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82">
+        <v>1100816</v>
+      </c>
+      <c r="D82" t="s">
+        <v>98</v>
+      </c>
+      <c r="E82" t="s">
+        <v>93</v>
+      </c>
+      <c r="F82" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82">
+        <v>60</v>
+      </c>
+      <c r="H82">
+        <v>4565.2999626954706</v>
+      </c>
+      <c r="I82">
+        <v>5798.6620718154518</v>
+      </c>
+      <c r="J82">
+        <v>6196.9732158071329</v>
+      </c>
+      <c r="K82">
+        <v>5567.6778419691009</v>
+      </c>
+      <c r="L82">
+        <v>7108.7119652384545</v>
+      </c>
+      <c r="M82">
+        <v>8170.6093153477641</v>
+      </c>
+      <c r="N82">
+        <v>8069.5243737494102</v>
+      </c>
+      <c r="O82">
+        <v>7916.5672212240906</v>
+      </c>
+      <c r="P82">
+        <v>9819.1832475443825</v>
+      </c>
+      <c r="Q82">
+        <v>9480.1142220384572</v>
+      </c>
+      <c r="R82">
+        <v>11203.14007487961</v>
+      </c>
+      <c r="S82">
+        <v>8072.1833337545404</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83">
+        <v>1100647</v>
+      </c>
+      <c r="D83" t="s">
+        <v>99</v>
+      </c>
+      <c r="E83" t="s">
+        <v>93</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83">
+        <v>90</v>
+      </c>
+      <c r="H83">
+        <v>1081.6897116372666</v>
+      </c>
+      <c r="I83">
+        <v>928.95630195180183</v>
+      </c>
+      <c r="J83">
+        <v>217.07231958020003</v>
+      </c>
+      <c r="K83">
+        <v>172.11250323246</v>
+      </c>
+      <c r="L83">
+        <v>0.60563130460000003</v>
+      </c>
+      <c r="M83">
+        <v>2.0596575505200003</v>
+      </c>
+      <c r="N83">
+        <v>10.277160756624001</v>
+      </c>
+      <c r="O83">
+        <v>1468.6656576791834</v>
+      </c>
+      <c r="P83">
+        <v>1502.8996804852848</v>
+      </c>
+      <c r="Q83">
+        <v>1479.6689921636842</v>
+      </c>
+      <c r="R83">
+        <v>1480.3724952964621</v>
+      </c>
+      <c r="S83">
+        <v>1400.547961511686</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84">
+        <v>1102101</v>
+      </c>
+      <c r="D84" t="s">
+        <v>100</v>
+      </c>
+      <c r="E84" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G84">
+        <v>90</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>5632</v>
+      </c>
+      <c r="P84">
+        <v>6902.2800000000007</v>
+      </c>
+      <c r="Q84">
+        <v>5360.8799999999992</v>
+      </c>
+      <c r="R84">
+        <v>6091.2199999999993</v>
+      </c>
+      <c r="S84">
+        <v>7326.0300000000007</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85">
+        <v>1102438</v>
+      </c>
+      <c r="D85" t="s">
+        <v>101</v>
+      </c>
+      <c r="E85" t="s">
+        <v>93</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85">
+        <v>60</v>
+      </c>
+      <c r="H85">
+        <v>24860.317445474113</v>
+      </c>
+      <c r="I85">
+        <v>19268.264500727426</v>
+      </c>
+      <c r="J85">
+        <v>23568.51048386193</v>
+      </c>
+      <c r="K85">
+        <v>18422.608459545689</v>
+      </c>
+      <c r="L85">
+        <v>20501.172793065063</v>
+      </c>
+      <c r="M85">
+        <v>21202.180122965761</v>
+      </c>
+      <c r="N85">
+        <v>19263.854029741713</v>
+      </c>
+      <c r="O85">
+        <v>15880.938638816308</v>
+      </c>
+      <c r="P85">
+        <v>16614.171690111838</v>
+      </c>
+      <c r="Q85">
+        <v>17544.575049544528</v>
+      </c>
+      <c r="R85">
+        <v>19224.888069412558</v>
+      </c>
+      <c r="S85">
+        <v>13597.680890501011</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>1102356</v>
+      </c>
+      <c r="D86" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86" t="s">
+        <v>93</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86">
+        <v>90</v>
+      </c>
+      <c r="H86">
+        <v>1110.6238356813601</v>
+      </c>
+      <c r="I86">
+        <v>1111.0848667463999</v>
+      </c>
+      <c r="J86">
+        <v>2667.3103643296499</v>
+      </c>
+      <c r="K86">
+        <v>2667.3103643296499</v>
+      </c>
+      <c r="L86">
+        <v>1173.54315651105</v>
+      </c>
+      <c r="M86">
+        <v>1173.54315651105</v>
+      </c>
+      <c r="N86">
+        <v>1173.084382798575</v>
+      </c>
+      <c r="O86">
+        <v>1173.54315651105</v>
+      </c>
+      <c r="P86">
+        <v>1173.54315651105</v>
+      </c>
+      <c r="Q86">
+        <v>981.31697098402492</v>
+      </c>
+      <c r="R86">
+        <v>1916.7565707205499</v>
+      </c>
+      <c r="S86">
+        <v>1366.2281157505499</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87">
+        <v>1102277</v>
+      </c>
+      <c r="D87" t="s">
+        <v>103</v>
+      </c>
+      <c r="E87" t="s">
+        <v>93</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87">
+        <v>60</v>
+      </c>
+      <c r="H87">
+        <v>180617.45144862114</v>
+      </c>
+      <c r="I87">
+        <v>186704.82906442627</v>
+      </c>
+      <c r="J87">
+        <v>213198.97548191791</v>
+      </c>
+      <c r="K87">
+        <v>196203.14758673264</v>
+      </c>
+      <c r="L87">
+        <v>210034.49433070351</v>
+      </c>
+      <c r="M87">
+        <v>203592.59893694401</v>
+      </c>
+      <c r="N87">
+        <v>211319.03780086371</v>
+      </c>
+      <c r="O87">
+        <v>217442.44035855014</v>
+      </c>
+      <c r="P87">
+        <v>230991.78493472631</v>
+      </c>
+      <c r="Q87">
+        <v>220489.82445794973</v>
+      </c>
+      <c r="R87">
+        <v>227298.74366961673</v>
+      </c>
+      <c r="S87">
+        <v>201412.6401912432</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88">
+        <v>1102411</v>
+      </c>
+      <c r="D88" t="s">
+        <v>104</v>
+      </c>
+      <c r="E88" t="s">
+        <v>93</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88">
+        <v>60</v>
+      </c>
+      <c r="H88">
+        <v>461.60587200000003</v>
+      </c>
+      <c r="I88">
+        <v>672.67515697200008</v>
+      </c>
+      <c r="J88">
+        <v>1129.7602729968751</v>
+      </c>
+      <c r="K88">
+        <v>258.62844135375002</v>
+      </c>
+      <c r="L88">
+        <v>288.19546933124997</v>
+      </c>
+      <c r="M88">
+        <v>278.72737610249999</v>
+      </c>
+      <c r="N88">
+        <v>303.643410915</v>
+      </c>
+      <c r="O88">
+        <v>319.17440594812496</v>
+      </c>
+      <c r="P88">
+        <v>267.76432078500005</v>
+      </c>
+      <c r="Q88">
+        <v>279.47485714687502</v>
+      </c>
+      <c r="R88">
+        <v>280.72065888750001</v>
+      </c>
+      <c r="S88">
+        <v>242.93133942187498</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89">
+        <v>1101980</v>
+      </c>
+      <c r="D89" t="s">
+        <v>105</v>
+      </c>
+      <c r="E89" t="s">
+        <v>106</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89">
+        <v>60</v>
+      </c>
+      <c r="H89">
+        <v>92751.920801233617</v>
+      </c>
+      <c r="I89">
+        <v>98191.988139406487</v>
+      </c>
+      <c r="J89">
+        <v>112746.38268807011</v>
+      </c>
+      <c r="K89">
+        <v>118798.48647040159</v>
+      </c>
+      <c r="L89">
+        <v>131721.40153093115</v>
+      </c>
+      <c r="M89">
+        <v>129551.11936633756</v>
+      </c>
+      <c r="N89">
+        <v>133964.76359744481</v>
+      </c>
+      <c r="O89">
+        <v>138273.44272642955</v>
+      </c>
+      <c r="P89">
+        <v>145663.51727889359</v>
+      </c>
+      <c r="Q89">
+        <v>144627.88261545476</v>
+      </c>
+      <c r="R89">
+        <v>168244.36145296268</v>
+      </c>
+      <c r="S89">
+        <v>138557.98268741599</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90">
+        <v>1100085</v>
+      </c>
+      <c r="D90" t="s">
+        <v>107</v>
+      </c>
+      <c r="E90" t="s">
+        <v>106</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90">
+        <v>60</v>
+      </c>
+      <c r="H90">
+        <v>19391.219115300002</v>
+      </c>
+      <c r="I90">
+        <v>23472.097444200001</v>
+      </c>
+      <c r="J90">
+        <v>26869.939105044305</v>
+      </c>
+      <c r="K90">
+        <v>19636.243797850002</v>
+      </c>
+      <c r="L90">
+        <v>20782.672615724998</v>
+      </c>
+      <c r="M90">
+        <v>24205.552314549997</v>
+      </c>
+      <c r="N90">
+        <v>22035.823302475001</v>
+      </c>
+      <c r="O90">
+        <v>20649.146470900003</v>
+      </c>
+      <c r="P90">
+        <v>20215.076112975003</v>
+      </c>
+      <c r="Q90">
+        <v>20280.893753224998</v>
+      </c>
+      <c r="R90">
+        <v>15766.205506824997</v>
+      </c>
+      <c r="S90">
+        <v>14128.870309150001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91">
+        <v>1100086</v>
+      </c>
+      <c r="D91" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" t="s">
+        <v>106</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91">
+        <v>60</v>
+      </c>
+      <c r="H91">
+        <v>188141.99078462052</v>
+      </c>
+      <c r="I91">
+        <v>180049.73351440532</v>
+      </c>
+      <c r="J91">
+        <v>209110.8777012869</v>
+      </c>
+      <c r="K91">
+        <v>175766.30375610356</v>
+      </c>
+      <c r="L91">
+        <v>185725.57304058361</v>
+      </c>
+      <c r="M91">
+        <v>176905.56114164784</v>
+      </c>
+      <c r="N91">
+        <v>182145.26406660862</v>
+      </c>
+      <c r="O91">
+        <v>182725.26830013757</v>
+      </c>
+      <c r="P91">
+        <v>198610.55722725569</v>
+      </c>
+      <c r="Q91">
+        <v>186863.660264476</v>
+      </c>
+      <c r="R91">
+        <v>178679.07967475965</v>
+      </c>
+      <c r="S91">
+        <v>158514.60166726352</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>1100658</v>
+      </c>
+      <c r="D92" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" t="s">
+        <v>110</v>
+      </c>
+      <c r="F92" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92">
+        <v>30</v>
+      </c>
+      <c r="H92">
+        <v>131562.58115900002</v>
+      </c>
+      <c r="I92">
+        <v>122678.23976540004</v>
+      </c>
+      <c r="J92">
+        <v>149879.84928380002</v>
+      </c>
+      <c r="K92">
+        <v>140553.15558595004</v>
+      </c>
+      <c r="L92">
+        <v>151703.16652135004</v>
+      </c>
+      <c r="M92">
+        <v>148363.56692149999</v>
+      </c>
+      <c r="N92">
+        <v>146810.79114975006</v>
+      </c>
+      <c r="O92">
+        <v>150612.70715405</v>
+      </c>
+      <c r="P92">
+        <v>162335.74775404998</v>
+      </c>
+      <c r="Q92">
+        <v>151680.99884324995</v>
+      </c>
+      <c r="R92">
+        <v>154406.22608040003</v>
+      </c>
+      <c r="S92">
+        <v>139363.42843349994</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
+  <autoFilter ref="A1:S92" xr:uid="{82D08FA1-B08E-4833-90E5-CCEB95A1E5DF}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -784,22 +6380,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4469690-FDEF-4FCF-A328-D845D2B02ED7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7E9EF34-F273-4258-B969-C01746EE07A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE4528B-3383-4599-B336-F4ACF217055C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB67A7A8-B774-4E9F-BB7D-FE263990813D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{560BED08-0C74-4424-954F-A9615049E364}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{016A1731-BD1C-4E90-9602-D659D3C6938D}"/>
 </file>